--- a/dataset_t6_grouped/results2/G4/G4_T8482_W0038F0001T0006Z000C1N36_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T8482_W0038F0001T0006Z000C1N36_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>42.31823504587902</v>
+        <v>6.876713194955341</v>
       </c>
       <c r="D2" t="n">
-        <v>19.34291988584848</v>
+        <v>3.143224481450378</v>
       </c>
       <c r="E2" t="n">
-        <v>8.219622203460359</v>
+        <v>1.335688608062308</v>
       </c>
       <c r="F2" t="n">
-        <v>11.71669502444631</v>
+        <v>1.903962941472525</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>42.04366322908001</v>
+        <v>6.832095274725502</v>
       </c>
       <c r="D3" t="n">
-        <v>43.33235904262474</v>
+        <v>7.041508344426521</v>
       </c>
       <c r="E3" t="n">
-        <v>8.219622203460359</v>
+        <v>1.335688608062308</v>
       </c>
       <c r="F3" t="n">
-        <v>11.71669502444631</v>
+        <v>1.903962941472525</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>33.39944478622699</v>
+        <v>5.427409777761887</v>
       </c>
       <c r="D4" t="n">
-        <v>13.99665138524211</v>
+        <v>2.274455850101844</v>
       </c>
       <c r="E4" t="n">
-        <v>8.219622203460359</v>
+        <v>1.335688608062308</v>
       </c>
       <c r="F4" t="n">
-        <v>11.71669502444631</v>
+        <v>1.903962941472525</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>37.94459345613743</v>
+        <v>6.165996436622332</v>
       </c>
       <c r="D5" t="n">
-        <v>25.92094208870731</v>
+        <v>4.212153089414937</v>
       </c>
       <c r="E5" t="n">
-        <v>8.219622203460359</v>
+        <v>1.335688608062308</v>
       </c>
       <c r="F5" t="n">
-        <v>11.71669502444631</v>
+        <v>1.903962941472525</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>37.90832663540706</v>
+        <v>6.160103078253647</v>
       </c>
       <c r="D6" t="n">
-        <v>39.0422651201707</v>
+        <v>6.344368082027739</v>
       </c>
       <c r="E6" t="n">
-        <v>8.219622203460359</v>
+        <v>1.335688608062308</v>
       </c>
       <c r="F6" t="n">
-        <v>11.71669502444631</v>
+        <v>1.903962941472525</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>13.18066326732802</v>
+        <v>2.141857780940803</v>
       </c>
       <c r="D7" t="n">
-        <v>12.31437234317896</v>
+        <v>2.001085505766581</v>
       </c>
       <c r="E7" t="n">
-        <v>8.219622203460359</v>
+        <v>1.335688608062308</v>
       </c>
       <c r="F7" t="n">
-        <v>11.71669502444631</v>
+        <v>1.903962941472525</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>37.2494962751106</v>
+        <v>6.053043144705473</v>
       </c>
       <c r="D8" t="n">
-        <v>7.229975586820364</v>
+        <v>1.174871032858309</v>
       </c>
       <c r="E8" t="n">
-        <v>8.219622203460359</v>
+        <v>1.335688608062308</v>
       </c>
       <c r="F8" t="n">
-        <v>11.71669502444631</v>
+        <v>1.903962941472525</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>36.95565755769083</v>
+        <v>6.00529435312476</v>
       </c>
       <c r="D9" t="n">
-        <v>25.5310083113383</v>
+        <v>4.148788850592474</v>
       </c>
       <c r="E9" t="n">
-        <v>8.219622203460359</v>
+        <v>1.335688608062308</v>
       </c>
       <c r="F9" t="n">
-        <v>11.71669502444631</v>
+        <v>1.903962941472525</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>34.49223948054365</v>
+        <v>5.604988915588343</v>
       </c>
       <c r="D10" t="n">
-        <v>33.59156123560373</v>
+        <v>5.458628700785606</v>
       </c>
       <c r="E10" t="n">
-        <v>8.219622203460359</v>
+        <v>1.335688608062308</v>
       </c>
       <c r="F10" t="n">
-        <v>11.71669502444631</v>
+        <v>1.903962941472525</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
